--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:46:42+00:00</t>
+    <t>2026-06-17T14:05:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:05:17+00:00</t>
+    <t>2026-06-17T14:38:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:38:50+00:00</t>
+    <t>2026-06-17T14:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T14:43:38+00:00</t>
+    <t>2026-06-17T15:09:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T15:09:02+00:00</t>
+    <t>2026-06-19T17:16:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T17:16:10+00:00</t>
+    <t>2026-06-26T10:38:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:38:02+00:00</t>
+    <t>2026-07-01T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:38:11+00:00</t>
+    <t>2026-07-01T08:43:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:43:34+00:00</t>
+    <t>2026-07-01T08:44:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:44:40+00:00</t>
+    <t>2026-07-01T08:45:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:45:35+00:00</t>
+    <t>2026-07-01T08:46:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:46:53+00:00</t>
+    <t>2026-07-01T08:57:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:57:39+00:00</t>
+    <t>2026-07-01T10:07:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:07:08+00:00</t>
+    <t>2026-07-01T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:07:52+00:00</t>
+    <t>2026-07-01T10:09:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:09:02+00:00</t>
+    <t>2026-07-01T12:36:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T12:36:12+00:00</t>
+    <t>2026-07-01T13:39:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:39:29+00:00</t>
+    <t>2026-07-02T11:54:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-SourcePatientInfo.xlsx
+++ b/main/ig/StructureDefinition-SourcePatientInfo.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-02T11:54:51+00:00</t>
+    <t>2026-07-16T07:22:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
